--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T08:52:11+00:00</t>
+    <t>2025-10-05T20:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-05T20:06:33+00:00</t>
+    <t>2025-10-05T20:13:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-05T20:13:42+00:00</t>
+    <t>2025-10-06T08:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,19 +112,19 @@
     <t>Ikke observert</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>241700002</t>
   </si>
   <si>
     <t>Tilstede</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -389,7 +390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -417,23 +418,61 @@
         <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="B2" t="s" s="2">
         <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-06T08:31:06+00:00</t>
+    <t>2025-10-09T18:55:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T18:55:57+00:00</t>
+    <t>2025-10-09T19:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,7 +94,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
   </si>
   <si>
     <t>Immutable</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T19:07:52+00:00</t>
+    <t>2025-10-09T19:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T19:37:50+00:00</t>
+    <t>2025-10-09T19:58:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-09T19:58:38+00:00</t>
+    <t>2026-01-29T20:13:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T20:13:56+00:00</t>
+    <t>2026-03-07T08:52:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T08:52:42+00:00</t>
+    <t>2026-03-07T09:02:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T09:02:29+00:00</t>
+    <t>2026-03-07T09:32:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T09:32:39+00:00</t>
+    <t>2026-03-07T09:45:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-07T09:45:24+00:00</t>
+    <t>2026-03-13T10:43:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
-    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T10:43:11+00:00</t>
+    <t>2026-05-08T07:00:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -94,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
+    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -112,6 +111,12 @@
     <t>Ikke observert</t>
   </si>
   <si>
+    <t>241700002</t>
+  </si>
+  <si>
+    <t>Tilstede</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -119,12 +124,6 @@
   </si>
   <si>
     <t>http://snomed.info/sct</t>
-  </si>
-  <si>
-    <t>241700002</t>
-  </si>
-  <si>
-    <t>Tilstede</t>
   </si>
 </sst>
 </file>
@@ -390,7 +389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -418,61 +417,23 @@
         <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B2" t="s" s="2">
+      <c r="B5" t="s" s="2">
         <v>36</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T07:00:45+00:00</t>
+    <t>2026-05-08T07:11:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T07:11:48+00:00</t>
+    <t>2026-05-08T08:25:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T08:25:34+00:00</t>
+    <t>2026-05-08T08:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T08:40:16+00:00</t>
+    <t>2026-05-08T09:06:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:06:57+00:00</t>
+    <t>2026-05-08T09:33:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:33:11+00:00</t>
+    <t>2026-05-08T10:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:00:47+00:00</t>
+    <t>2026-05-08T10:09:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:09:24+00:00</t>
+    <t>2026-05-08T11:19:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T11:19:22+00:00</t>
+    <t>2026-05-08T15:55:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +94,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This resource includes content from SNOMED Clinical Terms® (SNOMED CT®) which is copyright of the International Health Terminology Standards Development Organisation (IHTSDO). Implementers of these specifications must have the appropriate SNOMED CT Affiliate license - for more information contact http://www.snomed.org/snomed-ct/get-snomed-ct or info@snomed.org</t>
+    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
   </si>
   <si>
     <t>Immutable</t>
@@ -111,19 +112,19 @@
     <t>Ikke observert</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
+  </si>
+  <si>
     <t>241700002</t>
   </si>
   <si>
     <t>Tilstede</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -389,7 +390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -417,23 +418,61 @@
         <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B5" t="s" s="2">
+      <c r="B2" t="s" s="2">
         <v>36</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T15:55:34+00:00</t>
+    <t>2026-06-26T06:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
+++ b/VitalSigns/TestBuild/ValueSet-NoDomainVitalSignsSpontaneousBreathingValueSet.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T06:37:03+00:00</t>
+    <t>2026-06-26T06:47:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
